--- a/excel_data/series_dict.xlsx
+++ b/excel_data/series_dict.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FLC\Desktop\JavaScript\Gundam Card Web\gundam-card-web\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F0DFA0-FC47-411F-ADDE-C952AE469DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E3A15C-48A9-4C86-A5FC-467D089CB61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20390" yWindow="530" windowWidth="20380" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>日文原名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -369,6 +369,62 @@
   </si>
   <si>
     <t>排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新機動戦記ガンダムW Endless Waltz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>新機動戰記高達W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>無盡的華爾茲</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>新機動戰記鋼彈W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>無盡的華爾滋</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -715,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -849,46 +905,46 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
+      <c r="B11" t="s">
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="85.5" x14ac:dyDescent="5.0999999999999996">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>15</v>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -896,13 +952,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -910,13 +966,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -924,13 +980,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -938,13 +994,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -952,13 +1008,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -966,13 +1022,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -980,13 +1036,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -994,12 +1050,26 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>19</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>20</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>20</v>
       </c>
     </row>

--- a/excel_data/series_dict.xlsx
+++ b/excel_data/series_dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FLC\Desktop\JavaScript\Gundam Card Web\gundam-card-web\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E3A15C-48A9-4C86-A5FC-467D089CB61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E8F3BB-151A-4C58-9023-035BC4F953A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>日文原名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -425,6 +425,18 @@
       </rPr>
       <t>無盡的華爾滋</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機動戦士ガンダム 逆襲のシャア</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機動戰士高達 馬沙之反擊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機動戰士鋼彈 逆襲的夏亞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -835,18 +847,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -854,41 +866,41 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -896,69 +908,69 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>3</v>
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="85.5" x14ac:dyDescent="5.0999999999999996">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>15</v>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -966,13 +978,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -980,13 +992,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -994,13 +1006,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1008,13 +1020,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1022,13 +1034,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1036,13 +1048,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1050,13 +1062,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1064,12 +1076,26 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>20</v>
       </c>
     </row>
